--- a/artfynd/A 4864-2024 artfynd.xlsx
+++ b/artfynd/A 4864-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2900,6 +2900,779 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>114899426</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>565563</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6406702</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>114899463</v>
+      </c>
+      <c r="B23" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>565530</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6406699</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>114899394</v>
+      </c>
+      <c r="B24" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>565534</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6406697</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>114899436</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>565584</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6406695</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>114899411</v>
+      </c>
+      <c r="B26" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>565559</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6406692</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>114899418</v>
+      </c>
+      <c r="B27" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>565568</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6406699</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>114899365</v>
+      </c>
+      <c r="B28" t="n">
+        <v>97536</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>A 4864, Gårdspånga, Sm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>565525</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6406728</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Vimmerby</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Locknevi</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-02-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
